--- a/feature/fix-participant-status/ig/ValueSet-sas-valueset-categorieetablissement.xlsx
+++ b/feature/fix-participant-status/ig/ValueSet-sas-valueset-categorieetablissement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T07:59:14+00:00</t>
+    <t>2026-06-15T13:11:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t>604</t>
-  </si>
-  <si>
-    <t>CPTS</t>
   </si>
   <si>
     <t/>
@@ -397,24 +394,22 @@
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
